--- a/manya-react/public/content/sst/ple-sst.xlsx
+++ b/manya-react/public/content/sst/ple-sst.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\manya_app\content\sst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\manya_app\manya-react\public\content\sst\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -9656,6 +9656,7 @@
   <dimension ref="A1:J975"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="4" max="4" width="131.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="40.5703125" customWidth="1"/>
   </cols>
   <sheetData>
